--- a/trade_history.xlsx
+++ b/trade_history.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>24857</v>
+        <v>3331</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -500,32 +500,32 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>-196.15</t>
+          <t>-196.61</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0380, R2: 0.93)</t>
+          <t>(Eğim: 0.0328, R2: 0.71)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>24857</v>
+        <v>3331</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>48.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -535,32 +535,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>140,627.33</t>
+          <t>160,368.91</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P/L: %41.11 | Peak: 5.69</t>
+          <t>P/L: %60.89 | Peak: 43.92</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>27507</v>
+        <v>3020</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>53.10</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -570,67 +570,67 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>-280.18</t>
+          <t>-313.81</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0401, R2: 0.94)</t>
+          <t>(Eğim: 0.0727, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>TEHOL</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>27507</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TRHOL</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3020</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>47.80</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>147,887.34</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %5.57 | Peak: 5.55</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>143,753.47</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 53.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>28927</v>
+        <v>2735</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>52.55</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -640,67 +640,67 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-294.27</t>
+          <t>-258.22</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0338, R2: 0.89)</t>
+          <t>(Eğim: 0.0769, R2: 0.97)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>28927</v>
+        <v>2735</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224,881.40</t>
+          <t>156,007.37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P/L: %52.57 | Peak: 7.41</t>
+          <t>P/L: %8.94 | Peak: 63.60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>PAPIL</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>26220</v>
+        <v>5357</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,67 +710,67 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-444.40</t>
+          <t>-300.47</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0389, R2: 0.89)</t>
+          <t>(Eğim: 0.0490, R2: 0.97)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>PAPIL</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>26220</v>
+        <v>5357</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>235,824.58</t>
+          <t>179,334.74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P/L: %5.28 | Peak: 9.43</t>
+          <t>P/L: %15.38 | Peak: 36.40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>24369</v>
+        <v>4719</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -780,32 +780,32 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-470.91</t>
+          <t>-345.91</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0446, R2: 0.90)</t>
+          <t>(Eğim: 0.0325, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>24369</v>
+        <v>4719</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -815,32 +815,32 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>233,114.80</t>
+          <t>174,284.66</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-0.75 | Peak: 10.67</t>
+          <t>P/L: %-2.42 | Peak: 38.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>5836</v>
+        <v>1396</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -850,32 +850,32 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-441.21</t>
+          <t>-299.94</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0535, R2: 0.86)</t>
+          <t>(Eğim: 0.0400, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5836</v>
+        <v>1396</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47.80</t>
+          <t>133.17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -885,19 +885,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277,961.66</t>
+          <t>185,235.69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P/L: %19.68 | Peak: 53.10</t>
+          <t>P/L: %6.70 | Peak: 142.33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
@@ -906,11 +906,11 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>5289</v>
+        <v>1724</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>107.40</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -920,67 +920,67 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-531.16</t>
+          <t>-292.23</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0769, R2: 0.97)</t>
+          <t>(Eğim: 0.0316, R2: 0.53)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>TRHOL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>5289</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>57.25</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>1724</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>95.80</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>301,658.50</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %8.94 | Peak: 63.60</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>164,536.66</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-10.80 | Peak: 107.40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>PAPIL</t>
+          <t>VSNMD</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>10359</v>
+        <v>729</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>225.42</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -990,67 +990,67 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-598.90</t>
+          <t>-121.51</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0490, R2: 0.97)</t>
+          <t>(Eğim: 0.0340, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>PAPIL</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>10359</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33.60</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>346,767.36</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %15.38 | Peak: 36.40</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>VSNMD</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>202.92</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>147,508.25</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 225.42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>DERHL</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>9125</v>
+        <v>1873</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>78.75</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1060,67 +1060,67 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-676.14</t>
+          <t>-285.50</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0325, R2: 0.86)</t>
+          <t>(Eğim: 0.0468, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>9125</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>37.08</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>337,002.17</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-2.42 | Peak: 38.00</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DERHL</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>95.25</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>177,760.94</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %20.95 | Peak: 95.25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>DERHL</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>2700</v>
+        <v>1697</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>104.70</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1130,67 +1130,67 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-661.46</t>
+          <t>-270.30</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0366, R2: 0.85)</t>
+          <t>(Eğim: 0.0504, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>DERHL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2700</v>
+        <v>1697</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>133.17</t>
+          <t>124.60</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>358,182.53</t>
+          <t>210,753.00</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>P/L: %6.70 | Peak: 142.33</t>
+          <t>P/L: %19.01 | Peak: 138.40</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>VSNMD</t>
+          <t>DERHL</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1468</v>
+        <v>1584</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>243.94</t>
+          <t>133.00</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1200,67 +1200,67 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-633.23</t>
+          <t>-340.34</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0317, R2: 0.85)</t>
+          <t>(Eğim: 0.0465, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>VSNMD</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1468</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>225.42</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>329,618.14</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-7.59 | Peak: 251.90</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>DERHL</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1584</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>156.00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>246,269.45</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %17.29 | Peak: 161.60</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>3329</v>
+        <v>9427</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>99.00</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1270,67 +1270,67 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-612.00</t>
+          <t>-479.87</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0499, R2: 0.86)</t>
+          <t>(Eğim: 0.0367, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>TRHOL</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>3329</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>93.60</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>310,359.21</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-5.45 | Peak: 104.00</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>39.60</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>372,082.70</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %51.59 | Peak: 37.67</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>3258</v>
+        <v>8938</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>95.25</t>
+          <t>41.62</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1340,67 +1340,67 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-585.94</t>
+          <t>-705.64</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0431, R2: 0.91)</t>
+          <t>(Eğim: 0.0480, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>DERHL</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>3258</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>138.40</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>449,419.42</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %45.30 | Peak: 126.60</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>8938</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>37.46</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>333,464.52</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-10.00 | Peak: 41.62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>3606</v>
+        <v>9887</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>124.60</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1410,67 +1410,67 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>-786.79</t>
+          <t>-666.21</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0442, R2: 0.91)</t>
+          <t>(Eğim: 0.0417, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>DERHL</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>3606</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>161.60</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>580,777.38</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %29.70 | Peak: 160.80</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>9887</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>303,713.04</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-8.54 | Peak: 33.73</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>22348</v>
+        <v>8208</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,67 +1480,67 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-1,152.79</t>
+          <t>-590.35</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0349, R2: 0.83)</t>
+          <t>(Eğim: 0.0323, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>22348</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>37.67</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>838,901.17</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %44.94 | Peak: 34.24</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>EMKEL</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>8208</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>33.30</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>272,189.39</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-10.00 | Peak: 37.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>5601</v>
+        <v>5472</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>149.77</t>
+          <t>49.74</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,67 +1550,67 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-1,651.45</t>
+          <t>-532.25</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0457, R2: 0.82)</t>
+          <t>(Eğim: 0.0370, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>SMRVA</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>5601</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>140.79</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>785,313.83</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-6.00 | Peak: 149.77</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>5472</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>61.75</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>336,687.96</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %24.15 | Peak: 57.25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>18866</v>
+        <v>5017</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,67 +1620,67 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-1,554.02</t>
+          <t>-626.02</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0414, R2: 0.91)</t>
+          <t>(Eğim: 0.0491, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>18866</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>5017</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>703,800.00</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 41.62</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>349,861.60</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.32 | Peak: 72.50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>20867</v>
+        <v>5341</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>65.50</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1690,67 +1690,67 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-1,399.34</t>
+          <t>-673.57</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.84)</t>
+          <t>(Eğim: 0.0486, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>20867</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>641,008.05</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-8.54 | Peak: 33.73</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>5341</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>67.30</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>358,056.85</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %2.75 | Peak: 66.50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>17324</v>
+        <v>5487</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,67 +1760,67 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>-1,261.93</t>
+          <t>-685.95</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0311, R2: 0.93)</t>
+          <t>(Eğim: 0.0465, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>EMKEL</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>17324</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>574,473.48</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 37.00</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>5487</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>65.93</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>360,321.08</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %1.03 | Peak: 65.93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>11549</v>
+        <v>5165</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>49.74</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,67 +1830,67 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>-1,122.69</t>
+          <t>-658.19</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0375, R2: 0.89)</t>
+          <t>(Eğim: 0.0477, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>11549</v>
+        <v>5165</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>61.75</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>710,601.75</t>
+          <t>370,188.09</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>P/L: %24.15 | Peak: 57.25</t>
+          <t>P/L: %3.15 | Peak: 71.94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>10590</v>
+        <v>5133</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,67 +1900,67 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-1,408.41</t>
+          <t>-705.69</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0471, R2: 0.96)</t>
+          <t>(Eğim: 0.0447, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>10590</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>5133</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>64.91</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>738,408.99</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %4.32 | Peak: 72.50</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>331,823.77</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 72.11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>11273</v>
+        <v>5677</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>65.50</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,32 +1970,32 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-1,449.27</t>
+          <t>-624.96</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0396, R2: 0.93)</t>
+          <t>(Eğim: 0.0334, R2: 0.80)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>11273</v>
+        <v>5677</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>67.30</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2005,32 +2005,32 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>755,706.32</t>
+          <t>478,369.98</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>P/L: %2.75 | Peak: 66.50</t>
+          <t>P/L: %44.66 | Peak: 78.36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>11581</v>
+        <v>135132</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,67 +2040,67 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-1,465.25</t>
+          <t>-954.03</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0436, R2: 0.97)</t>
+          <t>(Eğim: 0.1330, R2: 0.56)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>11581</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>64.91</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>135132</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>748,782.89</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-0.52 | Peak: 72.11</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>487,245.44</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %2.26 | Peak: 3.54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>401707</v>
+        <v>139212</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,67 +2110,67 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-1,496.51</t>
+          <t>-971.04</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0392, R2: 0.93)</t>
+          <t>(Eğim: 0.1756, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>401707</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>731,355.23</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.93 | Peak: 1.87</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>139212</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>504,747.19</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.00 | Peak: 3.70</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>IDGYO</t>
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>202031</v>
+        <v>132479</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,32 +2180,32 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-1,459.67</t>
+          <t>-1,007.28</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1775, R2: 0.75)</t>
+          <t>(Eğim: 0.0306, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>IDGYO</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>202031</v>
+        <v>132479</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2215,32 +2215,32 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>704,234.61</t>
+          <t>468,352.56</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-3.31 | Peak: 3.62</t>
+          <t>P/L: %-6.82 | Peak: 3.81</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>3880</v>
+        <v>163759</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>181.50</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2250,32 +2250,32 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-1,393.83</t>
+          <t>-934.87</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0431, R2: 0.90)</t>
+          <t>(Eğim: 0.0359, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>3880</v>
+        <v>163759</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>170.90</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2285,32 +2285,32 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>660,371.96</t>
+          <t>451,770.34</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-5.84 | Peak: 184.00</t>
+          <t>P/L: %-3.15 | Peak: 2.86</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>IDGYO</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>186020</v>
+        <v>173757</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2320,67 +2320,67 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-1,319.77</t>
+          <t>-901.38</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0303, R2: 0.85)</t>
+          <t>(Eğim: 0.0327, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>IDGYO</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>186020</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>HUBVC</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>173757</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>657,730.48</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %0.00 | Peak: 3.81</t>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>432,622.33</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-3.85 | Peak: 2.63</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>HUBVC</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>229975</v>
+        <v>81015</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,67 +2390,67 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-1,313.45</t>
+          <t>-863.02</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.94)</t>
+          <t>(Eğim: 0.0765, R2: 0.98)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>HUBVC</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>229975</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>81015</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>6.79</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>634,443.23</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-3.15 | Peak: 2.86</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>548,128.64</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %27.15 | Peak: 6.95</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>36027</v>
+        <v>58373</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2460,67 +2460,67 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-1,261.13</t>
+          <t>-1,090.09</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0342, R2: 0.92)</t>
+          <t>(Eğim: 0.0399, R2: 0.81)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>36027</v>
+        <v>58373</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>17.20</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>617,163.96</t>
+          <t>537,780.26</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-2.33 | Peak: 17.99</t>
+          <t>P/L: %-1.49 | Peak: 9.79</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>YAYLA</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>8810</v>
+        <v>15234</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2530,67 +2530,67 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-1,210.84</t>
+          <t>-1,055.45</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0421, R2: 0.85)</t>
+          <t>(Eğim: 0.0303, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>YAYLA</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>8810</v>
+        <v>15234</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>43.50</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>660,415.75</t>
+          <t>660,298.19</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>P/L: %7.42 | Peak: 76.20</t>
+          <t>P/L: %23.23 | Peak: 45.02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>17887</v>
+        <v>73366</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2600,32 +2600,32 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-1,293.03</t>
+          <t>-1,316.40</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0318, R2: 0.82)</t>
+          <t>(Eğim: 0.0381, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>17887</v>
+        <v>73366</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2635,32 +2635,32 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>628,855.23</t>
+          <t>629,101.47</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-4.39 | Peak: 36.92</t>
+          <t>P/L: %-4.33 | Peak: 9.72</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>77254</v>
+        <v>25677</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2670,67 +2670,67 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-1,250.05</t>
+          <t>-1,243.20</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0537, R2: 0.96)</t>
+          <t>(Eğim: 0.0307, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>77254</v>
+        <v>25677</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>630,194.76</t>
+          <t>732,675.29</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>P/L: %0.61 | Peak: 8.40</t>
+          <t>P/L: %16.90 | Peak: 27.28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>70021</v>
+        <v>7732</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>94.75</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2740,32 +2740,32 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>-1,254.62</t>
+          <t>-1,396.93</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0381, R2: 0.94)</t>
+          <t>(Eğim: 0.0355, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>70021</v>
+        <v>7732</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2775,32 +2775,32 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>600,420.40</t>
+          <t>693,091.31</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-4.33 | Peak: 9.72</t>
+          <t>P/L: %-5.01 | Peak: 94.75</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>24506</v>
+        <v>23056</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2810,67 +2810,67 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>-1,177.39</t>
+          <t>-1,358.16</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0307, R2: 0.91)</t>
+          <t>(Eğim: 0.0309, R2: 0.80)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>24506</v>
+        <v>23056</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>699,270.73</t>
+          <t>759,348.77</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>P/L: %16.90 | Peak: 27.28</t>
+          <t>P/L: %9.98 | Peak: 33.06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>7380</v>
+        <v>20884</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2880,67 +2880,67 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>-1,382.78</t>
+          <t>-1,512.17</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0355, R2: 0.82)</t>
+          <t>(Eğim: 0.0379, R2: 0.79)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>ISGSY</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>7380</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>20884</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>47.32</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>661,488.82</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-5.01 | Peak: 94.75</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>984,742.24</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %30.14 | Peak: 48.34</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>22005</v>
+        <v>51476</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2950,67 +2950,67 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>-1,304.41</t>
+          <t>-1,963.07</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0309, R2: 0.80)</t>
+          <t>(Eğim: 0.1055, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>22005</v>
+        <v>51476</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>724,725.95</t>
+          <t>1,154,958.00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>P/L: %9.98 | Peak: 33.06</t>
+          <t>P/L: %17.72 | Peak: 23.14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>19931</v>
+        <v>9863</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>117.10</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3020,67 +3020,67 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>-1,414.60</t>
+          <t>-2,309.20</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0379, R2: 0.79)</t>
+          <t>(Eğim: 0.0375, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>19931</v>
+        <v>9863</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>128.60</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>939,834.04</t>
+          <t>1,263,535.89</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>P/L: %30.14 | Peak: 48.34</t>
+          <t>P/L: %9.82 | Peak: 122.50</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>8466</v>
+        <v>33874</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>111.00</t>
+          <t>37.30</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -3090,67 +3090,67 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>-1,771.41</t>
+          <t>-2,491.28</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0391, R2: 0.85)</t>
+          <t>(Eğim: 0.0376, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>8466</v>
+        <v>33874</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>111.00</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>936,075.14</t>
+          <t>1,265,243.17</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>P/L: %0.00 | Peak: 111.20</t>
+          <t>P/L: %0.54 | Peak: 38.30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>41566</v>
+        <v>31646</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -3160,32 +3160,32 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-1,863.33</t>
+          <t>-2,494.31</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1084, R2: 0.76)</t>
+          <t>(Eğim: 0.0340, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>41566</v>
+        <v>31646</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3195,32 +3195,32 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>908,270.81</t>
+          <t>1,134,483.18</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-2.58 | Peak: 22.52</t>
+          <t>P/L: %-9.95 | Peak: 39.98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>29779</v>
+        <v>35014</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>32.40</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -3230,67 +3230,67 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>-1,805.21</t>
+          <t>-2,239.38</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0505, R2: 0.95)</t>
+          <t>(Eğim: 0.0304, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>29779</v>
+        <v>35014</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>37.30</t>
+          <t>33.30</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1,106,729.96</t>
+          <t>1,161,394.86</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>P/L: %22.30 | Peak: 36.38</t>
+          <t>P/L: %2.78 | Peak: 34.00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>28896</v>
+        <v>2874</v>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>38.30</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3300,67 +3300,67 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>-2,200.25</t>
+          <t>-2,023.33</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0342, R2: 0.92)</t>
+          <t>(Eğim: 0.0337, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>IEYHO</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>28896</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>37.50</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>TRHOL</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2874</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>404.25</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>1,079,232.55</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-2.09 | Peak: 38.30</t>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1,157,467.54</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.06 | Peak: 418.00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>26994</v>
+        <v>2893</v>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3370,67 +3370,67 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>-2,146.00</t>
+          <t>-2,046.86</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0340, R2: 0.93)</t>
+          <t>(Eğim: 0.0433, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>26994</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>967,694.43</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.95 | Peak: 39.98</t>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>TRHOL</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>458.00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1,320,297.15</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %14.50 | Peak: 417.25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>29867</v>
+        <v>709</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>32.40</t>
+          <t>1861.00</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -3440,67 +3440,67 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>-1,931.80</t>
+          <t>-1,790.75</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0304, R2: 0.87)</t>
+          <t>(Eğim: 0.0547, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v>29867</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>990,650.14</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %2.78 | Peak: 34.00</t>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>1825.00</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>1,289,546.40</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.93 | Peak: 1862.00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>2452</v>
+        <v>682</v>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>404.00</t>
+          <t>1890.00</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -3510,67 +3510,67 @@
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-1,939.08</t>
+          <t>-2,011.56</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0337, R2: 0.78)</t>
+          <t>(Eğim: 0.0516, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>TRHOL</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v>2452</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>404.25</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>987,299.48</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %0.06 | Peak: 418.00</t>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>682</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>1856.00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>1,261,248.86</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.80 | Peak: 1890.00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>24682</v>
+        <v>714</v>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>1765.00</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3580,67 +3580,67 @@
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>-1,955.08</t>
+          <t>-1,481.56</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0347, R2: 0.96)</t>
+          <t>(Eğim: 0.0426, R2: 0.76)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>TEHOL</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>24682</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>41.50</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>1,020,299.31</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.75 | Peak: 41.30</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>714</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>1711.00</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>1,217,729.13</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-3.06 | Peak: 1765.00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>548</v>
+        <v>24305</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>1861.00</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3650,67 +3650,67 @@
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>-1,568.34</t>
+          <t>-2,386.69</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0549, R2: 0.94)</t>
+          <t>(Eğim: 0.0348, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>548</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>1825.00</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>996,531.46</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.93 | Peak: 1862.00</t>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>24305</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>56.15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1,359,609.64</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %12.08 | Peak: 56.30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>527</v>
+        <v>24278</v>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>1890.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3720,67 +3720,67 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>-1,490.60</t>
+          <t>-2,677.49</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0476, R2: 0.86)</t>
+          <t>(Eğim: 0.0325, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>527</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>1856.00</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>974,665.17</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.80 | Peak: 1890.00</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>24278</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>58.05</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>1,403,841.71</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %3.66 | Peak: 58.00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>19730</v>
+        <v>7799</v>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>49.40</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -3790,67 +3790,67 @@
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>-1,946.18</t>
+          <t>-2,785.93</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0327, R2: 0.91)</t>
+          <t>(Eğim: 0.0407, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>19730</v>
+        <v>7799</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>56.30</t>
+          <t>186.80</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1,106,631.21</t>
+          <t>1,451,153.59</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>P/L: %13.97 | Peak: 55.85</t>
+          <t>P/L: %3.78 | Peak: 207.50</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>19708</v>
+        <v>7534</v>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>56.15</t>
+          <t>192.60</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3860,67 +3860,67 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-2,186.23</t>
+          <t>-2,796.95</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0331, R2: 0.93)</t>
+          <t>(Eğim: 0.0522, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>IEYHO</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>19708</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>58.00</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>1,138,591.64</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.29 | Peak: 57.70</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>7534</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>178.80</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>1,341,588.11</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-7.17 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>6325</v>
+        <v>9382</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3930,67 +3930,67 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>-2,185.36</t>
+          <t>-2,660.18</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0407, R2: 0.82)</t>
+          <t>(Eğim: 0.0360, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>6325</v>
+        <v>9382</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>186.80</t>
+          <t>171.99</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1,176,961.64</t>
+          <t>1,607,743.41</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>P/L: %3.78 | Peak: 207.50</t>
+          <t>P/L: %20.28 | Peak: 179.89</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>6110</v>
+        <v>9468</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>192.60</t>
+          <t>169.79</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -4000,67 +4000,67 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>-2,177.97</t>
+          <t>-3,065.25</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0522, R2: 0.95)</t>
+          <t>(Eğim: 0.0351, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>6110</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>178.80</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>1,088,105.11</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-7.17 | Peak: 192.60</t>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ALKLC</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>9468</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>226.10</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2,133,368.18</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %33.16 | Peak: 227.00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>7609</v>
+        <v>6843</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>311.75</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -4070,67 +4070,67 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>-2,108.62</t>
+          <t>-4,203.68</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0360, R2: 0.89)</t>
+          <t>(Eğim: 0.0375, R2: 0.98)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>ALKLC</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v>7609</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>171.99</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>1,303,962.68</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %20.28 | Peak: 179.89</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>6843</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>306.25</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>2,087,273.73</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.76 | Peak: 330.50</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>7679</v>
+        <v>6363</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>169.79</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -4140,32 +4140,32 @@
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>-2,480.05</t>
+          <t>-3,964.40</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0351, R2: 0.89)</t>
+          <t>(Eğim: 0.0311, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>7679</v>
+        <v>6363</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>226.10</t>
+          <t>442.00</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4175,19 +4175,19 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>1,730,269.46</t>
+          <t>2,802,856.71</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>P/L: %33.16 | Peak: 227.00</t>
+          <t>P/L: %34.76 | Peak: 436.75</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
@@ -4196,11 +4196,11 @@
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>5550</v>
+        <v>7007</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>311.75</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -4210,19 +4210,19 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>-3,403.47</t>
+          <t>-5,548.89</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0375, R2: 0.98)</t>
+          <t>(Eğim: 0.0332, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4231,11 +4231,11 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>5550</v>
+        <v>7007</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>306.25</t>
+          <t>369.00</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -4245,32 +4245,32 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>1,692,884.66</t>
+          <t>2,574,862.94</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-1.76 | Peak: 330.50</t>
+          <t>P/L: %-7.75 | Peak: 400.00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>5527</v>
+        <v>327590</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>306.25</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -4280,67 +4280,67 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>-3,144.38</t>
+          <t>-5,144.22</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0301, R2: 0.92)</t>
+          <t>(Eğim: 0.0321, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5527</v>
+        <v>327590</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>436.75</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2,405,945.03</t>
+          <t>2,646,297.06</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>P/L: %42.61 | Peak: 436.25</t>
+          <t>P/L: %3.18 | Peak: 8.35</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>5443</v>
+        <v>296670</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>442.00</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -4350,32 +4350,32 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>-4,672.58</t>
+          <t>-5,291.95</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0317, R2: 0.91)</t>
+          <t>(Eğim: 0.0300, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>5443</v>
+        <v>296670</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2,168,173.02</t>
+          <t>2,629,790.21</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.50 | Peak: 442.00</t>
+          <t>P/L: %-0.22 | Peak: 9.27</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>258115</v>
+        <v>26807</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>98.10</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4420,32 +4420,32 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>-4,329.21</t>
+          <t>-5,235.99</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0315, R2: 0.89)</t>
+          <t>(Eğim: 0.0337, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>258115</v>
+        <v>26807</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2,020,397.16</t>
+          <t>2,536,335.68</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-6.43 | Peak: 8.40</t>
+          <t>P/L: %-3.16 | Peak: 98.10</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>247597</v>
+        <v>76812</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4490,67 +4490,67 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>-4,035.11</t>
+          <t>-5,069.26</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0317, R2: 0.90)</t>
+          <t>(Eğim: 0.0418, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>EDATA</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>247597</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>76812</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>1,999,960.45</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-0.61 | Peak: 8.35</t>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2,677,973.90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %6.00 | Peak: 36.32</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>20920</v>
+        <v>69557</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>95.60</t>
+          <t>38.50</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4560,54 +4560,54 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>-3,991.42</t>
+          <t>-5,326.48</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.97)</t>
+          <t>(Eğim: 0.0406, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>20920</v>
+        <v>69557</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>99.75</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2,078,605.04</t>
+          <t>2,933,826.82</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>P/L: %4.34 | Peak: 104.80</t>
+          <t>P/L: %9.97 | Peak: 42.34</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
@@ -4616,11 +4616,11 @@
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>67751</v>
+        <v>63011</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -4630,67 +4630,67 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>-4,152.86</t>
+          <t>-5,833.01</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0411, R2: 0.85)</t>
+          <t>(Eğim: 0.0401, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>SEGMN</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>67751</v>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="C121" s="3" t="n">
+        <v>63011</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>46.08</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2,362,389.57</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %14.08 | Peak: 36.32</t>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>2,891,906.89</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.03 | Peak: 51.20</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>61360</v>
+        <v>5016</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>576.50</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -4700,67 +4700,67 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>-4,695.15</t>
+          <t>-5,600.56</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0406, R2: 0.85)</t>
+          <t>(Eğim: 0.0317, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>61360</v>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2,588,091.29</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %9.97 | Peak: 42.34</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>5016</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>519.00</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>2,592,496.83</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.97 | Peak: 576.50</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>55586</v>
+        <v>29460</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>88.00</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -4770,47 +4770,152 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>-5,169.11</t>
+          <t>-5,168.13</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0401, R2: 0.85)</t>
+          <t>(Eğim: 0.0313, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>55586</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>2,551,111.06</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.03 | Peak: 51.20</t>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>29460</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>103.30</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>3,031,963.53</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %17.39 | Peak: 100.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>28986</v>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>104.60</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>-6,035.90</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0346, R2: 0.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>28986</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>113.70</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>3,283,080.80</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %8.70 | Peak: 113.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>ODINE</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>5162</v>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>636.00</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>-6,517.27</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0346, R2: 0.94)</t>
         </is>
       </c>
     </row>

--- a/trade_history.xlsx
+++ b/trade_history.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>3331</v>
+        <v>12269</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -500,67 +500,67 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>-196.61</t>
+          <t>-192.33</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0328, R2: 0.71)</t>
+          <t>(Eğim: 0.0452, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3331</v>
+        <v>12269</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>48.30</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>160,368.91</t>
+          <t>97,151.14</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P/L: %60.89 | Peak: 43.92</t>
+          <t>P/L: %-2.45 | Peak: 8.15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>3020</v>
+        <v>3754</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>53.10</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -570,67 +570,67 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>-313.81</t>
+          <t>-177.88</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0727, R2: 0.94)</t>
+          <t>(Eğim: 0.0392, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3020</v>
+        <v>3754</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>47.80</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>143,753.47</t>
+          <t>128,120.74</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.98 | Peak: 53.10</t>
+          <t>P/L: %32.35 | Peak: 31.14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>VANGD</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>2735</v>
+        <v>3273</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>39.14</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -640,32 +640,32 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-258.22</t>
+          <t>-240.69</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0769, R2: 0.97)</t>
+          <t>(Eğim: 0.0340, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>VANGD</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2735</v>
+        <v>3273</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -675,32 +675,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156,007.37</t>
+          <t>115,457.10</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P/L: %8.94 | Peak: 63.60</t>
+          <t>P/L: %-9.50 | Peak: 39.14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>PAPIL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>5357</v>
+        <v>2773</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>29.12</t>
+          <t>41.62</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,67 +710,67 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-300.47</t>
+          <t>-199.88</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0490, R2: 0.97)</t>
+          <t>(Eğim: 0.0480, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PAPIL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5357</v>
+        <v>2773</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>179,334.74</t>
+          <t>103,475.87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P/L: %15.38 | Peak: 36.40</t>
+          <t>P/L: %-10.00 | Peak: 41.62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>4719</v>
+        <v>3067</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -780,67 +780,67 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-345.91</t>
+          <t>-173.26</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0325, R2: 0.86)</t>
+          <t>(Eğim: 0.0417, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>4719</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>37.08</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3067</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>174,284.66</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-2.42 | Peak: 38.00</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94,246.81</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-8.54 | Peak: 33.73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>1396</v>
+        <v>2547</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -850,32 +850,32 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-299.94</t>
+          <t>-180.67</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0400, R2: 0.91)</t>
+          <t>(Eğim: 0.0323, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1396</v>
+        <v>2547</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>133.17</t>
+          <t>33.30</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -885,32 +885,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185,235.69</t>
+          <t>84,464.80</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P/L: %6.70 | Peak: 142.33</t>
+          <t>P/L: %-10.00 | Peak: 37.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>1724</v>
+        <v>83463</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>107.40</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -920,67 +920,67 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-292.23</t>
+          <t>-168.68</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0316, R2: 0.53)</t>
+          <t>(Eğim: 0.0310, R2: 0.67)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>TRHOL</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1724</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>95.80</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>164,536.66</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-10.80 | Peak: 107.40</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82,294.43</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-2.17 | Peak: 1.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>VSNMD</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>729</v>
+        <v>92051</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>225.42</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -990,67 +990,67 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-121.51</t>
+          <t>-163.75</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0340, R2: 0.83)</t>
+          <t>(Eğim: 0.0364, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VSNMD</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>729</v>
+        <v>92051</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>202.92</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>147,508.25</t>
+          <t>99,052.50</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.98 | Peak: 225.42</t>
+          <t>P/L: %20.81 | Peak: 1.08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>1873</v>
+        <v>83377</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1060,67 +1060,67 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-285.50</t>
+          <t>-197.47</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0468, R2: 0.86)</t>
+          <t>(Eğim: 0.0479, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>DERHL</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1873</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>95.25</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>177,760.94</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %20.95 | Peak: 95.25</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>83377</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>118,793.17</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %20.37 | Peak: 1.34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1697</v>
+        <v>88917</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>104.70</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1130,67 +1130,67 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-270.30</t>
+          <t>-237.52</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0504, R2: 0.90)</t>
+          <t>(Eğim: 0.0560, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>DERHL</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1697</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>124.60</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210,753.00</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %19.01 | Peak: 138.40</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>88917</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>142,987.49</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %20.81 | Peak: 1.61</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1584</v>
+        <v>2225</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>133.00</t>
+          <t>64.24</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1200,54 +1200,54 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-340.34</t>
+          <t>-226.81</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0465, R2: 0.91)</t>
+          <t>(Eğim: 0.0428, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>DERHL</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>1584</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>156.00</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>246,269.45</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %17.29 | Peak: 161.60</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2225</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>65.25</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>144,664.08</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %1.58 | Peak: 65.25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>9427</v>
+        <v>2194</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>65.93</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1270,54 +1270,54 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-479.87</t>
+          <t>-264.66</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0367, R2: 0.84)</t>
+          <t>(Eğim: 0.0479, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>TERA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>9427</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>39.60</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>372,082.70</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %51.59 | Peak: 37.67</t>
+      <c r="C25" s="3" t="n">
+        <v>2194</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>71.94</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>157,264.23</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %9.13 | Peak: 71.94</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
@@ -1326,11 +1326,11 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>8938</v>
+        <v>2180</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1340,54 +1340,54 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-705.64</t>
+          <t>-255.43</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0480, R2: 0.93)</t>
+          <t>(Eğim: 0.0447, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>TERA</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>8938</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="n">
+        <v>2180</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>64.91</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>333,464.52</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 41.62</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>140,970.80</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 72.11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
@@ -1396,11 +1396,11 @@
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>9887</v>
+        <v>2412</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1410,19 +1410,19 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>-666.21</t>
+          <t>-277.46</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0417, R2: 0.88)</t>
+          <t>(Eğim: 0.0334, R2: 0.80)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1431,46 +1431,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9887</v>
+        <v>2412</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>303,713.04</t>
+          <t>203,234.22</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-8.54 | Peak: 33.73</t>
+          <t>P/L: %44.66 | Peak: 78.36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>8208</v>
+        <v>57410</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,67 +1480,67 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-590.35</t>
+          <t>-403.64</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0323, R2: 0.95)</t>
+          <t>(Eğim: 0.1330, R2: 0.56)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8208</v>
+        <v>57410</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>33.30</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>272,189.39</t>
+          <t>207,004.90</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-10.00 | Peak: 37.00</t>
+          <t>P/L: %2.26 | Peak: 3.54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>5472</v>
+        <v>59144</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>49.74</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,67 +1550,67 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-532.25</t>
+          <t>-413.10</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0370, R2: 0.84)</t>
+          <t>(Eğim: 0.1756, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>5472</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>61.75</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>59144</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>336,687.96</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %24.15 | Peak: 57.25</t>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>214,440.49</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %4.00 | Peak: 3.70</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>IDGYO</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>5017</v>
+        <v>56283</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,32 +1620,32 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-626.02</t>
+          <t>-426.61</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0491, R2: 0.95)</t>
+          <t>(Eğim: 0.0306, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>IDGYO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5017</v>
+        <v>56283</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1655,32 +1655,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>349,861.60</t>
+          <t>198,978.43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>P/L: %4.32 | Peak: 72.50</t>
+          <t>P/L: %-6.82 | Peak: 3.81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>5341</v>
+        <v>34013</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>65.50</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1690,67 +1690,67 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-673.57</t>
+          <t>-395.57</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0486, R2: 0.94)</t>
+          <t>(Eğim: 0.0358, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>5341</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>67.30</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>358,056.85</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %2.75 | Peak: 66.50</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>CRDFA</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>34013</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>198,861.42</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %0.34 | Peak: 6.19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>5487</v>
+        <v>33762</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,67 +1760,67 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>-685.95</t>
+          <t>-394.47</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0465, R2: 0.95)</t>
+          <t>(Eğim: 0.0354, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5487</v>
+        <v>33762</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>65.93</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>360,321.08</t>
+          <t>192,787.19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>P/L: %1.03 | Peak: 65.93</t>
+          <t>P/L: %-2.66 | Peak: 6.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>5165</v>
+        <v>2752</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,67 +1830,67 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>-658.19</t>
+          <t>-375.98</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0477, R2: 0.96)</t>
+          <t>(Eğim: 0.0420, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>5165</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>71.94</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>EMKEL</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2752</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>76.20</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>VOLUME STOP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>370,188.09</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.15 | Peak: 71.94</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>208,907.01</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %8.78 | Peak: 76.20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>YAYLA</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>5133</v>
+        <v>5726</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>36.48</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,67 +1900,67 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-705.69</t>
+          <t>-395.24</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0447, R2: 0.95)</t>
+          <t>(Eğim: 0.0324, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>5133</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>64.91</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>5726</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>35.30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>331,823.77</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.98 | Peak: 72.11</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>201,328.30</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-3.23 | Peak: 36.92</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>5677</v>
+        <v>24733</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,67 +1970,67 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-624.96</t>
+          <t>-400.98</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0334, R2: 0.80)</t>
+          <t>(Eğim: 0.0537, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>5677</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>84.54</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>478,369.98</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %44.66 | Peak: 78.36</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>24733</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>201,757.16</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %0.61 | Peak: 8.40</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>135132</v>
+        <v>22417</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,67 +2040,67 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-954.03</t>
+          <t>-399.35</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1330, R2: 0.56)</t>
+          <t>(Eğim: 0.0381, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>135132</v>
+        <v>22417</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>487,245.44</t>
+          <t>192,224.99</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>P/L: %2.26 | Peak: 3.54</t>
+          <t>P/L: %-4.33 | Peak: 9.72</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>139212</v>
+        <v>44890</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,67 +2110,67 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-971.04</t>
+          <t>-383.38</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1756, R2: 0.75)</t>
+          <t>(Eğim: 0.0307, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>KGYO</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>139212</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>CEMZY</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>44890</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>504,747.19</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %4.00 | Peak: 3.70</t>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>223,873.04</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %16.90 | Peak: 4.77</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>IDGYO</t>
+          <t>RODRG</t>
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>132479</v>
+        <v>6588</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,67 +2180,67 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-1,007.28</t>
+          <t>-434.92</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0306, R2: 0.83)</t>
+          <t>(Eğim: 0.0374, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>IDGYO</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>132479</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>RODRG</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>6588</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>31.40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>468,352.56</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-6.82 | Peak: 3.81</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>206,014.55</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-7.59 | Peak: 34.80</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>HUBVC</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>163759</v>
+        <v>12883</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2250,67 +2250,67 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-934.87</t>
+          <t>-396.61</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0359, R2: 0.94)</t>
+          <t>(Eğim: 0.0308, R2: 0.80)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>HUBVC</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>163759</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>12883</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>451,770.34</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-3.15 | Peak: 2.86</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>184,747.55</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.94 | Peak: 15.99</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>HUBVC</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>173757</v>
+        <v>11663</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2320,67 +2320,67 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-901.38</t>
+          <t>-363.85</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0327, R2: 0.88)</t>
+          <t>(Eğim: 0.0352, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>HUBVC</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>173757</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>11663</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14.26</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>432,622.33</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-3.85 | Peak: 2.63</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>165,617.90</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.97 | Peak: 15.84</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>81015</v>
+        <v>10789</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,32 +2390,32 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-863.02</t>
+          <t>-324.48</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0765, R2: 0.98)</t>
+          <t>(Eğim: 0.0358, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>81015</v>
+        <v>10789</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>13.82</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2425,32 +2425,32 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>548,128.64</t>
+          <t>148,481.29</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>P/L: %27.15 | Peak: 6.95</t>
+          <t>P/L: %-9.97 | Peak: 15.35</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>58373</v>
+        <v>11974</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2460,67 +2460,67 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-1,090.09</t>
+          <t>-293.26</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0399, R2: 0.81)</t>
+          <t>(Eğim: 0.0317, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>58373</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>CRDFA</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>11974</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>537,780.26</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.49 | Peak: 9.79</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>143,107.37</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-3.23 | Peak: 13.33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15234</v>
+        <v>13250</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2530,67 +2530,67 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-1,055.45</t>
+          <t>-278.84</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0303, R2: 0.78)</t>
+          <t>(Eğim: 0.0304, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>YAYLA</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>15234</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>43.50</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>660,298.19</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %23.23 | Peak: 45.02</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CRDFA</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>13250</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>146,502.02</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %2.78 | Peak: 11.33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>DOGUB</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>73366</v>
+        <v>3603</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2600,67 +2600,67 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-1,316.40</t>
+          <t>-288.96</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0381, R2: 0.94)</t>
+          <t>(Eğim: 0.0337, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>DOGUB</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>73366</v>
+        <v>3603</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>629,101.47</t>
+          <t>234,696.18</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-4.33 | Peak: 9.72</t>
+          <t>P/L: %60.72 | Peak: 59.45</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>DOGUB</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>25677</v>
+        <v>3988</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>58.85</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2670,67 +2670,67 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-1,243.20</t>
+          <t>-467.01</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0307, R2: 0.91)</t>
+          <t>(Eğim: 0.0596, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>DOGUB</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>25677</v>
+        <v>3988</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>732,675.29</t>
+          <t>210,474.27</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>P/L: %16.90 | Peak: 27.28</t>
+          <t>P/L: %-9.94 | Peak: 58.85</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>ISGSY</t>
+          <t>BURVA</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>7732</v>
+        <v>659</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>319.25</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2740,67 +2740,67 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>-1,396.93</t>
+          <t>-332.26</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0355, R2: 0.82)</t>
+          <t>(Eğim: 0.0488, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>ISGSY</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>7732</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>BURVA</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>314.50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>693,091.31</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-5.01 | Peak: 94.75</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>206,508.73</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-1.49 | Peak: 351.00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>BURVA</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>23056</v>
+        <v>666</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>309.75</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2810,67 +2810,67 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>-1,358.16</t>
+          <t>-197.35</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0309, R2: 0.80)</t>
+          <t>(Eğim: 0.0496, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>BURVA</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>23056</v>
+        <v>666</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>279.00</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>759,348.77</t>
+          <t>185,245.02</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>P/L: %9.98 | Peak: 33.06</t>
+          <t>P/L: %-9.93 | Peak: 309.75</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>20884</v>
+        <v>14271</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2880,32 +2880,32 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>-1,512.17</t>
+          <t>-363.03</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0379, R2: 0.79)</t>
+          <t>(Eğim: 0.0305, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>20884</v>
+        <v>14271</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>984,742.24</t>
+          <t>166,131.30</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>P/L: %30.14 | Peak: 48.34</t>
+          <t>P/L: %-9.94 | Peak: 12.98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>51476</v>
+        <v>15776</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>-1,963.07</t>
+          <t>-322.22</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1055, R2: 0.75)</t>
+          <t>(Eğim: 0.0343, R2: 0.81)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>51476</v>
+        <v>15776</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2985,32 +2985,32 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1,154,958.00</t>
+          <t>159,326.49</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>P/L: %17.72 | Peak: 23.14</t>
+          <t>P/L: %-3.70 | Peak: 10.53</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>9863</v>
+        <v>15102</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>117.10</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3020,67 +3020,67 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>-2,309.20</t>
+          <t>-318.27</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0375, R2: 0.83)</t>
+          <t>(Eğim: 0.0328, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>9863</v>
+        <v>15102</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>128.60</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1,263,535.89</t>
+          <t>142,863.79</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>P/L: %9.82 | Peak: 122.50</t>
+          <t>P/L: %-9.95 | Peak: 10.55</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>33874</v>
+        <v>840</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>37.30</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -3090,67 +3090,67 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>-2,491.28</t>
+          <t>-221.81</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0376, R2: 0.90)</t>
+          <t>(Eğim: 0.0311, R2: 0.67)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>IEYHO</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>33874</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>37.50</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>1,265,243.17</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %0.54 | Peak: 38.30</t>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>840</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>186.80</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>156,376.37</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %9.88 | Peak: 207.50</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>31646</v>
+        <v>811</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>192.60</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -3160,67 +3160,67 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-2,494.31</t>
+          <t>-134.63</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0340, R2: 0.93)</t>
+          <t>(Eğim: 0.0522, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>31646</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>178.80</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>1,134,483.18</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.95 | Peak: 39.98</t>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>144,582.16</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-7.17 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>35014</v>
+        <v>1011</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>32.40</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -3230,67 +3230,67 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>-2,239.38</t>
+          <t>-273.42</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0304, R2: 0.87)</t>
+          <t>(Eğim: 0.0360, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>35014</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>1,161,394.86</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %2.78 | Peak: 34.00</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>ALKLC</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>171.99</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>173,262.93</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %20.28 | Peak: 179.89</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>VKFYO</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>2874</v>
+        <v>4853</v>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>404.00</t>
+          <t>35.70</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3300,67 +3300,67 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>-2,023.33</t>
+          <t>-335.68</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0337, R2: 0.78)</t>
+          <t>(Eğim: 0.0416, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>TRHOL</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>2874</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>404.25</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1,157,467.54</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %0.06 | Peak: 418.00</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>VKFYO</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>4853</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>38.72</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>187,196.67</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %8.46 | Peak: 43.02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>VKFYO</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>2893</v>
+        <v>4565</v>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3370,67 +3370,67 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>-2,046.86</t>
+          <t>-342.66</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0433, R2: 0.94)</t>
+          <t>(Eğim: 0.0308, R2: 0.70)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>VKFYO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2893</v>
+        <v>4565</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>458.00</t>
+          <t>38.90</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1,320,297.15</t>
+          <t>176,880.69</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>P/L: %14.50 | Peak: 417.25</t>
+          <t>P/L: %-5.12 | Peak: 41.00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>BURVA</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>709</v>
+        <v>272</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>1861.00</t>
+          <t>649.00</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -3440,67 +3440,67 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>-1,790.75</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0547, R2: 0.92)</t>
+          <t>(Eğim: 0.0308, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>1825.00</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>1,289,546.40</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.93 | Peak: 1862.00</t>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>BURVA</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>630.00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>171,016.92</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-2.93 | Peak: 649.00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>682</v>
+        <v>20359</v>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>1890.00</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -3510,67 +3510,67 @@
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-2,011.56</t>
+          <t>-340.71</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0516, R2: 0.88)</t>
+          <t>(Eğim: 0.0313, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>682</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>1856.00</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>1,261,248.86</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.80 | Peak: 1890.00</t>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>EDATA</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>20359</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>159,360.99</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-6.43 | Peak: 8.40</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>714</v>
+        <v>19529</v>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>1765.00</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3580,67 +3580,67 @@
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>-1,481.56</t>
+          <t>-314.36</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0426, R2: 0.76)</t>
+          <t>(Eğim: 0.0324, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>714</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>1711.00</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>EDATA</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>19529</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>1,217,729.13</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-3.06 | Peak: 1765.00</t>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>157,749.07</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-0.61 | Peak: 8.35</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>24305</v>
+        <v>17684</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3650,67 +3650,67 @@
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>-2,386.69</t>
+          <t>-307.70</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0348, R2: 0.93)</t>
+          <t>(Eğim: 0.0300, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>24305</v>
+        <v>17684</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>56.15</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1,359,609.64</t>
+          <t>156,765.12</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>P/L: %12.08 | Peak: 56.30</t>
+          <t>P/L: %-0.22 | Peak: 9.27</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>24278</v>
+        <v>1598</v>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>98.10</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3720,67 +3720,67 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>-2,677.49</t>
+          <t>-312.20</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0325, R2: 0.92)</t>
+          <t>(Eğim: 0.0337, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>24278</v>
+        <v>1598</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1,403,841.71</t>
+          <t>151,194.18</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>P/L: %3.66 | Peak: 58.00</t>
+          <t>P/L: %-3.16 | Peak: 98.10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>7799</v>
+        <v>4578</v>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -3790,67 +3790,67 @@
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>-2,785.93</t>
+          <t>-273.72</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0407, R2: 0.82)</t>
+          <t>(Eğim: 0.0418, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>7799</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>186.80</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>4578</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>1,451,153.59</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.78 | Peak: 207.50</t>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>159,635.82</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %6.00 | Peak: 36.32</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>7534</v>
+        <v>4146</v>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>192.60</t>
+          <t>38.50</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3860,67 +3860,67 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-2,796.95</t>
+          <t>-304.42</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0522, R2: 0.95)</t>
+          <t>(Eğim: 0.0406, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>7534</v>
+        <v>4146</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>178.80</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>1,341,588.11</t>
+          <t>174,886.14</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-7.17 | Peak: 192.60</t>
+          <t>P/L: %9.97 | Peak: 42.34</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>9382</v>
+        <v>3756</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3930,67 +3930,67 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>-2,660.18</t>
+          <t>-342.99</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0360, R2: 0.89)</t>
+          <t>(Eğim: 0.0401, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>9382</v>
+        <v>3756</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>171.99</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1,607,743.41</t>
+          <t>172,387.35</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>P/L: %20.28 | Peak: 179.89</t>
+          <t>P/L: %-1.03 | Peak: 51.20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>9468</v>
+        <v>3603</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>169.79</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -4000,67 +4000,67 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>-3,065.25</t>
+          <t>-324.91</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0351, R2: 0.89)</t>
+          <t>(Eğim: 0.0350, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>9468</v>
+        <v>3603</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>226.10</t>
+          <t>46.20</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2,133,368.18</t>
+          <t>165,800.78</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>P/L: %33.16 | Peak: 227.00</t>
+          <t>P/L: %-3.43 | Peak: 47.84</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>6843</v>
+        <v>7948</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>311.75</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -4070,67 +4070,67 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>-4,203.68</t>
+          <t>-326.10</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0375, R2: 0.98)</t>
+          <t>(Eğim: 0.0438, R2: 0.97)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>6843</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>306.25</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ZERGY</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>7948</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>2,087,273.73</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.76 | Peak: 330.50</t>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>148,638.82</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.97 | Peak: 20.86</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>6363</v>
+        <v>14361</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -4140,67 +4140,67 @@
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>-3,964.40</t>
+          <t>-294.81</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0311, R2: 0.95)</t>
+          <t>(Eğim: 0.0364, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>6363</v>
+        <v>14361</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>442.00</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2,802,856.71</t>
+          <t>133,282.02</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>P/L: %34.76 | Peak: 436.75</t>
+          <t>P/L: %-9.95 | Peak: 10.35</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>NIBAS</t>
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>7007</v>
+        <v>20042</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -4210,67 +4210,67 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>-5,548.89</t>
+          <t>-263.84</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0332, R2: 0.93)</t>
+          <t>(Eğim: 0.0326, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>7007</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>369.00</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>NIBAS</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>20042</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>6.32</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>2,574,862.94</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-7.75 | Peak: 400.00</t>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>126,148.27</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-4.96 | Peak: 6.65</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>NIBAS</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>327590</v>
+        <v>19288</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -4280,67 +4280,67 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>-5,144.22</t>
+          <t>-247.54</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0321, R2: 0.88)</t>
+          <t>(Eğim: 0.0363, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>EDATA</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>327590</v>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>NIBAS</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>19288</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2,646,297.06</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.18 | Peak: 8.35</t>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>127,761.14</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %1.68 | Peak: 7.10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>296670</v>
+        <v>85</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -4350,67 +4350,67 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>-5,291.95</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0300, R2: 0.84)</t>
+          <t>(Eğim: 0.0376, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>296670</v>
+        <v>85</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>1731.00</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2,629,790.21</t>
+          <t>146,846.87</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-0.22 | Peak: 9.27</t>
+          <t>P/L: %15.40 | Peak: 1730.00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>ODINE</t>
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>26807</v>
+        <v>229</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>98.10</t>
+          <t>641.00</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4420,32 +4420,32 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>-5,235.99</t>
+          <t>-235.71</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0337, R2: 0.96)</t>
+          <t>(Eğim: 0.0323, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>ODINE</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>26807</v>
+        <v>229</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2,536,335.68</t>
+          <t>148,316.59</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-3.16 | Peak: 98.10</t>
+          <t>P/L: %1.40 | Peak: 679.00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>76812</v>
+        <v>202</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>731.50</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4490,67 +4490,67 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>-5,069.26</t>
+          <t>258.06</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0418, R2: 0.86)</t>
+          <t>(Eğim: 0.0438, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>76812</v>
+        <v>202</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>719.00</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2,677,973.90</t>
+          <t>145,205.59</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>P/L: %6.00 | Peak: 36.32</t>
+          <t>P/L: %-1.71 | Peak: 731.50</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>69557</v>
+        <v>224</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>647.50</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4560,67 +4560,67 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>-5,326.48</t>
+          <t>-124.49</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0406, R2: 0.85)</t>
+          <t>(Eğim: 0.0343, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>69557</v>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2,933,826.82</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %9.97 | Peak: 42.34</t>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>831.50</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>185,758.99</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %28.42 | Peak: 760.00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>63011</v>
+        <v>1255</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>147.97</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -4630,67 +4630,67 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>-5,833.01</t>
+          <t>-318.79</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0401, R2: 0.85)</t>
+          <t>(Eğim: 0.0302, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>63011</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>NETCD</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>1255</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>142.75</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>2,891,906.89</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-1.03 | Peak: 51.20</t>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>178,474.94</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-3.53 | Peak: 158.52</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>5016</v>
+        <v>1266</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>576.50</t>
+          <t>140.90</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -4700,67 +4700,67 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>-5,600.56</t>
+          <t>-261.21</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0317, R2: 0.89)</t>
+          <t>(Eğim: 0.0303, R2: 0.81)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>5016</v>
+        <v>1266</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>519.00</t>
+          <t>148.20</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2,592,496.83</t>
+          <t>186,984.74</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.97 | Peak: 576.50</t>
+          <t>P/L: %5.18 | Peak: 149.80</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>29460</v>
+        <v>1275</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>146.60</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -4770,67 +4770,67 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>-5,168.13</t>
+          <t>-304.10</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0313, R2: 0.87)</t>
+          <t>(Eğim: 0.0421, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>29460</v>
+        <v>1275</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>103.30</t>
+          <t>139.60</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>3,031,963.53</t>
+          <t>177,329.93</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>P/L: %17.39 | Peak: 100.70</t>
+          <t>P/L: %-4.77 | Peak: 147.50</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>28986</v>
+        <v>1222</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>104.60</t>
+          <t>145.00</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -4840,67 +4840,67 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>-6,035.90</t>
+          <t>-214.45</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0346, R2: 0.95)</t>
+          <t>(Eğim: 0.0327, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>28986</v>
+        <v>1222</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>113.70</t>
+          <t>130.20</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>3,283,080.80</t>
+          <t>158,571.74</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>P/L: %8.70 | Peak: 113.70</t>
+          <t>P/L: %-10.21 | Peak: 145.00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>ODINE</t>
+          <t>AYCES</t>
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>5162</v>
+        <v>121</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>636.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4910,12 +4910,47 @@
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>-6,517.27</t>
+          <t>957.14</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0346, R2: 0.94)</t>
+          <t>(Eğim: 0.0320, R2: 0.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>AYCES</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>1170.00</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>142,244.00</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-10.00 | Peak: 1300.00</t>
         </is>
       </c>
     </row>

--- a/trade_history.xlsx
+++ b/trade_history.xlsx
@@ -552,15 +552,15 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>3754</v>
+        <v>13199</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -570,67 +570,67 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>-177.88</t>
+          <t>-187.79</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0392, R2: 0.86)</t>
+          <t>(Eğim: 0.0390, R2: 0.79)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3754</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>128,120.74</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %32.35 | Peak: 31.14</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MOBTL</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>13199</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6.84</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89,912.81</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-7.07 | Peak: 7.36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>VANGD</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>3273</v>
+        <v>3441</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>39.14</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -640,47 +640,47 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-240.69</t>
+          <t>-154.49</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0340, R2: 0.88)</t>
+          <t>(Eğim: 0.0367, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>VANGD</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>3273</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>115,457.10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.50 | Peak: 39.14</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3441</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>39.60</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>135,836.58</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %51.59 | Peak: 37.67</t>
         </is>
       </c>
     </row>
@@ -692,15 +692,15 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>2773</v>
+        <v>4936</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,47 +710,47 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-199.88</t>
+          <t>-249.40</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0480, R2: 0.93)</t>
+          <t>(Eğim: 0.0462, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>2773</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>103,475.87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 41.62</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>SMRVA</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4936</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>28.84</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>141,830.13</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %4.82 | Peak: 28.84</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>3067</v>
+        <v>4205</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-173.26</t>
+          <t>-277.66</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3067</v>
+        <v>4205</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,246.81</t>
+          <t>129,176.65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>2547</v>
+        <v>3491</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-180.67</t>
+          <t>-248.68</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2547</v>
+        <v>3491</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,464.80</t>
+          <t>115,769.12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>83463</v>
+        <v>114396</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-168.68</t>
+          <t>-231.17</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>83463</v>
+        <v>114396</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,294.43</t>
+          <t>112,794.37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>92051</v>
+        <v>126168</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-163.75</t>
+          <t>-225.41</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>92051</v>
+        <v>126168</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>99,052.50</t>
+          <t>135,763.51</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>83377</v>
+        <v>114279</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-197.47</t>
+          <t>-271.46</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>83377</v>
+        <v>114279</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>118,793.17</t>
+          <t>162,820.66</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>88917</v>
+        <v>121871</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-237.52</t>
+          <t>-324.63</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>88917</v>
+        <v>121871</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>142,987.49</t>
+          <t>195,981.76</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>2225</v>
+        <v>3050</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-226.81</t>
+          <t>-334.47</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2225</v>
+        <v>3050</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>144,664.08</t>
+          <t>198,280.00</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>2194</v>
+        <v>3007</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-264.66</t>
+          <t>-352.95</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2194</v>
+        <v>3007</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>157,264.23</t>
+          <t>215,549.23</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2180</v>
+        <v>2989</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-255.43</t>
+          <t>-426.13</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2180</v>
+        <v>2989</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>140,970.80</t>
+          <t>193,209.28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>2412</v>
+        <v>3305</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>-277.46</t>
+          <t>-333.62</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2412</v>
+        <v>3305</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>203,234.22</t>
+          <t>278,524.63</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
@@ -1466,11 +1466,11 @@
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>57410</v>
+        <v>78902</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-403.64</t>
+          <t>-556.48</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1330, R2: 0.56)</t>
+          <t>(Eğim: 0.1490, R2: 0.63)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>KGYO</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>57410</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="n">
+        <v>78902</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>207,004.90</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %2.26 | Peak: 3.54</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>275,048.21</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-0.85 | Peak: 3.62</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>59144</v>
+        <v>76829</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,19 +1550,19 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-413.10</t>
+          <t>-549.70</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1756, R2: 0.75)</t>
+          <t>(Eğim: 0.1705, R2: 0.72)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>59144</v>
+        <v>76829</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1585,32 +1585,32 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>214,440.49</t>
+          <t>281,615.56</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>P/L: %4.00 | Peak: 3.70</t>
+          <t>P/L: %2.79 | Peak: 3.70</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>IDGYO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>56283</v>
+        <v>52835</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,54 +1620,54 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-426.61</t>
+          <t>-558.21</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0306, R2: 0.83)</t>
+          <t>(Eğim: 0.0342, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>IDGYO</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>56283</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>CRDFA</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>52835</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>198,978.43</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-6.82 | Peak: 3.81</t>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>308,962.95</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %10.13 | Peak: 6.19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
@@ -1676,11 +1676,11 @@
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>34013</v>
+        <v>52455</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1690,67 +1690,67 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-395.57</t>
+          <t>-614.91</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0358, R2: 0.92)</t>
+          <t>(Eğim: 0.0354, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>CRDFA</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>34013</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>5.87</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="n">
+        <v>52455</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>198,861.42</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %0.34 | Peak: 6.19</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>299,525.60</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-2.66 | Peak: 6.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>33762</v>
+        <v>4275</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,67 +1760,67 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>-394.47</t>
+          <t>-537.09</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0354, R2: 0.92)</t>
+          <t>(Eğim: 0.0420, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>33762</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>5.73</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>192,787.19</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-2.66 | Peak: 6.00</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>EMKEL</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>4275</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>76.20</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>324,566.38</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %8.78 | Peak: 76.20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>YAYLA</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>2752</v>
+        <v>8897</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>36.48</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,67 +1830,67 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>-375.98</t>
+          <t>-645.30</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0420, R2: 0.85)</t>
+          <t>(Eğim: 0.0324, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>EMKEL</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>2752</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>76.20</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>208,907.01</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %8.78 | Peak: 76.20</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>YAYLA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>8897</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>35.30</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>312,790.67</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-3.23 | Peak: 36.92</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>5726</v>
+        <v>38426</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,54 +1900,54 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-395.24</t>
+          <t>-622.56</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0324, R2: 0.83)</t>
+          <t>(Eğim: 0.0537, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>YAYLA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>5726</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>35.30</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>38426</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>201,328.30</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-3.23 | Peak: 36.92</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>313,456.94</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %0.61 | Peak: 8.40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>24733</v>
+        <v>34828</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,67 +1970,67 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-400.98</t>
+          <t>-621.96</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0537, R2: 0.96)</t>
+          <t>(Eğim: 0.0381, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PEKGY</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>24733</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="n">
+        <v>34828</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>8.61</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>201,757.16</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %0.61 | Peak: 8.40</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>298,647.37</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-4.33 | Peak: 9.72</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>22417</v>
+        <v>69743</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,67 +2040,67 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-399.35</t>
+          <t>-597.14</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0381, R2: 0.94)</t>
+          <t>(Eğim: 0.0307, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>22417</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>8.61</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>192,224.99</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-4.33 | Peak: 9.72</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>CEMZY</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>69743</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>347,817.11</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %16.90 | Peak: 4.77</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>RODRG</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>44890</v>
+        <v>10235</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,54 +2110,54 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-383.38</t>
+          <t>-663.75</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0307, R2: 0.91)</t>
+          <t>(Eğim: 0.0374, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>CEMZY</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>44890</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>223,873.04</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %16.90 | Peak: 4.77</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>RODRG</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>10235</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>31.40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>320,072.49</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-7.59 | Peak: 34.80</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
@@ -2166,11 +2166,11 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>6588</v>
+        <v>9983</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-434.92</t>
+          <t>-622.62</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0374, R2: 0.91)</t>
+          <t>(Eğim: 0.0323, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2201,11 +2201,11 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>6588</v>
+        <v>9983</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>31.40</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>206,014.55</t>
+          <t>286,910.55</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-7.59 | Peak: 34.80</t>
+          <t>P/L: %-9.98 | Peak: 32.06</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>12883</v>
+        <v>17943</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-396.61</t>
+          <t>-571.83</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>12883</v>
+        <v>17943</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>184,747.55</t>
+          <t>257,290.60</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>11663</v>
+        <v>16243</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-363.85</t>
+          <t>-513.10</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>11663</v>
+        <v>16243</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>165,617.90</t>
+          <t>230,648.83</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
@@ -2376,11 +2376,11 @@
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>10789</v>
+        <v>16835</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,47 +2390,47 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-324.48</t>
+          <t>-451.94</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0358, R2: 0.85)</t>
+          <t>(Eğim: 0.0355, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>ALKA</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>10789</v>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>16835</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>13.82</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>148,481.29</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.97 | Peak: 15.35</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>231,742.43</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %0.88 | Peak: 15.35</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>11974</v>
+        <v>18688</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-293.26</t>
+          <t>-452.22</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>11974</v>
+        <v>18688</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>143,107.37</t>
+          <t>223,355.27</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>13250</v>
+        <v>20681</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-278.84</t>
+          <t>-446.25</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>13250</v>
+        <v>20681</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>146,502.02</t>
+          <t>228,653.74</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>3603</v>
+        <v>5623</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-288.96</t>
+          <t>-434.70</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>3603</v>
+        <v>5623</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>234,696.18</t>
+          <t>366,293.42</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>3988</v>
+        <v>6224</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-467.01</t>
+          <t>-721.54</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>3988</v>
+        <v>6224</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>210,474.27</t>
+          <t>328,490.72</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2722,15 +2722,15 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>DOGUB</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>659</v>
+        <v>6886</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>319.25</t>
+          <t>47.70</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2740,54 +2740,54 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>-332.26</t>
+          <t>-628.41</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0488, R2: 0.94)</t>
+          <t>(Eğim: 0.0500, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>BURVA</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>659</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>314.50</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>206,508.73</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-1.49 | Peak: 351.00</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>DOGUB</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>6886</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>62.75</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>430,603.89</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %31.55 | Peak: 69.70</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>666</v>
+        <v>1713</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>309.75</t>
+          <t>251.25</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2810,19 +2810,19 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>-197.35</t>
+          <t>-648.14</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0496, R2: 0.92)</t>
+          <t>(Eğim: 0.0385, R2: 0.74)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2831,33 +2831,33 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>666</v>
+        <v>1713</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>279.00</t>
+          <t>247.90</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>185,245.02</t>
+          <t>423,155.25</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.93 | Peak: 309.75</t>
+          <t>P/L: %-1.33 | Peak: 251.25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
@@ -2866,11 +2866,11 @@
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>14271</v>
+        <v>40185</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2880,19 +2880,19 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>-363.03</t>
+          <t>-839.09</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0305, R2: 0.75)</t>
+          <t>(Eğim: 0.0343, R2: 0.81)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2901,11 +2901,11 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>14271</v>
+        <v>40185</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2915,19 +2915,19 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>166,131.30</t>
+          <t>405,821.87</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.94 | Peak: 12.98</t>
+          <t>P/L: %-3.70 | Peak: 10.53</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
@@ -2936,11 +2936,11 @@
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>15776</v>
+        <v>38466</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2950,19 +2950,19 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>-322.22</t>
+          <t>-806.07</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.81)</t>
+          <t>(Eğim: 0.0328, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>15776</v>
+        <v>38466</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2985,32 +2985,32 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>159,326.49</t>
+          <t>363,890.08</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-3.70 | Peak: 10.53</t>
+          <t>P/L: %-9.95 | Peak: 10.55</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>15102</v>
+        <v>2140</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3020,54 +3020,54 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>-318.27</t>
+          <t>-637.52</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0328, R2: 0.78)</t>
+          <t>(Eğim: 0.0311, R2: 0.67)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>15102</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>142,863.79</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.95 | Peak: 10.55</t>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>186.80</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>398,314.98</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %9.88 | Peak: 207.50</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
@@ -3076,11 +3076,11 @@
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>840</v>
+        <v>2068</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>192.60</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -3090,54 +3090,54 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>-221.81</t>
+          <t>-778.42</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0311, R2: 0.67)</t>
+          <t>(Eğim: 0.0522, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>GUNDG</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
-        <v>840</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>186.80</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>156,376.37</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %9.88 | Peak: 207.50</t>
+      <c r="C77" s="2" t="n">
+        <v>2068</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>178.80</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>368,240.46</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-7.17 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
@@ -3146,11 +3146,11 @@
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>811</v>
+        <v>1873</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>192.60</t>
+          <t>196.60</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -3160,67 +3160,67 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-134.63</t>
+          <t>-727.81</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0522, R2: 0.95)</t>
+          <t>(Eğim: 0.0483, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>GUNDG</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>811</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>178.80</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>229.90</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>144,582.16</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-7.17 | Peak: 192.60</t>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>429,013.67</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %16.94 | Peak: 255.25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>ALKLC</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>1011</v>
+        <v>1963</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>218.50</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -3230,67 +3230,67 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>-273.42</t>
+          <t>-759.66</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0360, R2: 0.89)</t>
+          <t>(Eğim: 0.0362, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>ALKLC</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>171.99</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>173,262.93</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %20.28 | Peak: 179.89</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>196.70</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>384,590.19</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 218.50</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>VKFYO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>4853</v>
+        <v>27102</v>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3300,67 +3300,67 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>-335.68</t>
+          <t>-756.33</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0416, R2: 0.86)</t>
+          <t>(Eğim: 0.0367, R2: 0.77)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>VKFYO</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>4853</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>38.72</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>187,196.67</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %8.46 | Peak: 43.02</t>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>27102</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>344,914.49</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %-9.94 | Peak: 14.19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>VKFYO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>4565</v>
+        <v>5501</v>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3370,47 +3370,47 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>-342.66</t>
+          <t>-688.04</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0308, R2: 0.70)</t>
+          <t>(Eğim: 0.0302, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>VKFYO</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>4565</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>38.90</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>176,880.69</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-5.12 | Peak: 41.00</t>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>ARMGD</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>5501</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>72.45</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>397,062.30</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %15.55 | Peak: 65.90</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>272</v>
+        <v>611</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-269.78</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>272</v>
+        <v>611</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>171,016.92</t>
+          <t>383,890.36</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>20359</v>
+        <v>45701</v>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-340.71</t>
+          <t>-765.79</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>20359</v>
+        <v>45701</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>159,360.99</t>
+          <t>357,725.65</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>19529</v>
+        <v>43838</v>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>-314.36</t>
+          <t>-707.86</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>19529</v>
+        <v>43838</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>157,749.07</t>
+          <t>354,107.25</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>17684</v>
+        <v>39698</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>-307.70</t>
+          <t>-707.12</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>17684</v>
+        <v>39698</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>156,765.12</t>
+          <t>351,898.44</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>1598</v>
+        <v>3587</v>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>-312.20</t>
+          <t>-690.02</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1598</v>
+        <v>3587</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>151,194.18</t>
+          <t>339,393.45</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>4578</v>
+        <v>10278</v>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>-273.72</t>
+          <t>-664.88</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>4578</v>
+        <v>10278</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>159,635.82</t>
+          <t>358,345.66</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>4146</v>
+        <v>9307</v>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-304.42</t>
+          <t>-690.48</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4146</v>
+        <v>9307</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>174,886.14</t>
+          <t>392,579.79</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>3756</v>
+        <v>8431</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>-342.99</t>
+          <t>-752.68</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>3756</v>
+        <v>8431</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>172,387.35</t>
+          <t>386,970.82</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>3603</v>
+        <v>8088</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>-324.91</t>
+          <t>-732.96</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>3603</v>
+        <v>8088</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>165,800.78</t>
+          <t>372,185.31</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>7948</v>
+        <v>17842</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>-326.10</t>
+          <t>-743.19</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>7948</v>
+        <v>17842</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>148,638.82</t>
+          <t>333,659.44</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4122,15 +4122,15 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>14361</v>
+        <v>17938</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -4140,47 +4140,47 @@
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>-294.81</t>
+          <t>-654.66</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0364, R2: 0.87)</t>
+          <t>(Eğim: 0.0379, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>ATLAS</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v>14361</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>9.32</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>ZERGY</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>17938</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>133,282.02</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.95 | Peak: 10.35</t>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>343,961.22</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %3.49 | Peak: 20.46</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>20042</v>
+        <v>51723</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>-263.84</t>
+          <t>-684.65</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>20042</v>
+        <v>51723</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>126,148.27</t>
+          <t>325,550.94</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>19288</v>
+        <v>49778</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>-247.54</t>
+          <t>-648.27</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>19288</v>
+        <v>49778</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>127,761.14</t>
+          <t>329,713.39</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>556.39</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>146,846.87</t>
+          <t>378,887.21</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>229</v>
+        <v>591</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>-235.71</t>
+          <t>-701.45</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>229</v>
+        <v>591</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>148,316.59</t>
+          <t>382,680.25</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>202</v>
+        <v>523</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>258.06</t>
+          <t>-659.40</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>202</v>
+        <v>523</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>145,205.59</t>
+          <t>374,625.52</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>224</v>
+        <v>578</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>-124.49</t>
+          <t>-377.99</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>224</v>
+        <v>578</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>185,758.99</t>
+          <t>479,267.80</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>1255</v>
+        <v>3238</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>-318.79</t>
+          <t>-827.71</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>1255</v>
+        <v>3238</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>178,474.94</t>
+          <t>460,474.36</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1266</v>
+        <v>3268</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>-261.21</t>
+          <t>-907.74</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>1266</v>
+        <v>3268</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>186,984.74</t>
+          <t>482,441.21</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>1275</v>
+        <v>3290</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>-304.10</t>
+          <t>-837.44</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>1275</v>
+        <v>3290</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>177,329.93</t>
+          <t>457,528.01</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>1222</v>
+        <v>3155</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>-214.45</t>
+          <t>-861.94</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>1222</v>
+        <v>3155</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>158,571.74</t>
+          <t>409,097.49</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -4892,15 +4892,15 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>AYCES</t>
+          <t>SVGYO</t>
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>121</v>
+        <v>23551</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4910,47 +4910,47 @@
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>957.14</t>
+          <t>-801.56</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0320, R2: 0.95)</t>
+          <t>(Eğim: 0.0438, R2: 0.81)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>AYCES</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>1170.00</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>142,244.00</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 1300.00</t>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>SVGYO</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>23551</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>454,233.92</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %11.46 | Peak: 19.23</t>
         </is>
       </c>
     </row>

--- a/trade_history.xlsx
+++ b/trade_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="İşlem Geçmişi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İşlem Geçmişi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>12269</v>
+        <v>1746</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -500,67 +500,67 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>-192.33</t>
+          <t>-158.42</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0452, R2: 0.87)</t>
+          <t>(Eğim: 0.0435, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>12269</v>
+        <v>1746</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>72.50</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>97,151.14</t>
+          <t>126,173.41</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-2.45 | Peak: 8.15</t>
+          <t>P/L: %26.64 | Peak: 72.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>13199</v>
+        <v>1802</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -570,67 +570,67 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>-187.79</t>
+          <t>-218.87</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0390, R2: 0.79)</t>
+          <t>(Eğim: 0.0440, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MOBTL</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>13199</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6.84</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>65.50</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>89,912.81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-7.07 | Peak: 7.36</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>117,576.07</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-6.43 | Peak: 70.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>3441</v>
+        <v>1801</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -640,67 +640,67 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-154.49</t>
+          <t>-174.21</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0367, R2: 0.84)</t>
+          <t>(Eğim: 0.0355, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>3441</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>39.60</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1801</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66.25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>135,836.58</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %51.59 | Peak: 37.67</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118,903.41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %1.53 | Peak: 67.30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>4936</v>
+        <v>1803</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>65.93</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,67 +710,67 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-249.40</t>
+          <t>-197.10</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0462, R2: 0.75)</t>
+          <t>(Eğim: 0.0426, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4936</v>
+        <v>1803</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>141,830.13</t>
+          <t>116,606.06</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>P/L: %4.82 | Peak: 28.84</t>
+          <t>P/L: %-1.54 | Peak: 72.11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>4205</v>
+        <v>62556</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -780,67 +780,67 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-277.66</t>
+          <t>-231.53</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0417, R2: 0.88)</t>
+          <t>(Eğim: 0.0392, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4205</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>62556</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129,176.65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-8.54 | Peak: 33.73</t>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>113,892.13</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.93 | Peak: 1.87</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3491</v>
+        <v>13717</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -850,67 +850,67 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-248.68</t>
+          <t>-221.40</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0323, R2: 0.95)</t>
+          <t>(Eğim: 0.0557, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>EMKEL</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>3491</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>GEDIK</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>13717</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>115,769.12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-10.00 | Peak: 37.00</t>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>102,128.29</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.95 | Peak: 8.30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>114396</v>
+        <v>14579</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -920,67 +920,67 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-231.17</t>
+          <t>-203.48</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0310, R2: 0.67)</t>
+          <t>(Eğim: 0.0445, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>114396</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>GEDIK</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>14579</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>112,794.37</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-2.17 | Peak: 1.01</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>91,534.24</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.99 | Peak: 7.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>126168</v>
+        <v>25930</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -990,67 +990,67 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-225.41</t>
+          <t>-181.72</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0364, R2: 0.75)</t>
+          <t>(Eğim: 0.1490, R2: 0.63)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>126168</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>135,763.51</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %20.81 | Peak: 1.08</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>25930</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93,497.14</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %2.55 | Peak: 3.62</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>114279</v>
+        <v>26713</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1060,67 +1060,67 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-271.46</t>
+          <t>-185.35</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0479, R2: 0.90)</t>
+          <t>(Eğim: 0.1706, R2: 0.72)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>114279</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>26713</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>162,820.66</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %20.37 | Peak: 1.34</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>96,855.50</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.00 | Peak: 3.70</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>121871</v>
+        <v>18892</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1130,67 +1130,67 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-324.63</t>
+          <t>-191.18</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0560, R2: 0.96)</t>
+          <t>(Eğim: 0.0329, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>121871</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>195,981.76</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %20.81 | Peak: 1.61</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CRDFA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>18892</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>110,483.07</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %14.50 | Peak: 6.19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>3050</v>
+        <v>18757</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1200,67 +1200,67 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-334.47</t>
+          <t>-216.62</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0428, R2: 0.88)</t>
+          <t>(Eğim: 0.0321, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3050</v>
+        <v>18757</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>198,280.00</t>
+          <t>107,108.43</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>P/L: %1.58 | Peak: 65.25</t>
+          <t>P/L: %-2.66 | Peak: 6.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>3007</v>
+        <v>1529</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>65.93</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1270,67 +1270,67 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-352.95</t>
+          <t>-212.24</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0479, R2: 0.96)</t>
+          <t>(Eğim: 0.0421, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>3007</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>71.94</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>EMKEL</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>75.25</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>VOLUME STOP</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>215,549.23</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %9.13 | Peak: 71.94</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>114,614.90</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %7.42 | Peak: 76.20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2989</v>
+        <v>23146</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1340,67 +1340,67 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-426.13</t>
+          <t>-224.31</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0447, R2: 0.95)</t>
+          <t>(Eğim: 0.0320, R2: 0.68)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>2989</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>64.91</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>23146</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>193,209.28</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.98 | Peak: 72.11</t>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>109,333.92</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-4.22 | Peak: 4.95</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>3305</v>
+        <v>13431</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1410,67 +1410,67 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>-333.62</t>
+          <t>-213.09</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0334, R2: 0.80)</t>
+          <t>(Eğim: 0.0537, R2: 0.96)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>TERA</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>3305</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>84.54</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>278,524.63</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %44.66 | Peak: 78.36</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>13431</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>109,566.80</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.61 | Peak: 8.40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>78902</v>
+        <v>12174</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,67 +1480,67 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-556.48</t>
+          <t>-218.33</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1490, R2: 0.63)</t>
+          <t>(Eğim: 0.0381, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>KGYO</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>78902</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>275,048.21</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-0.85 | Peak: 3.62</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>12174</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>8.61</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>104,390.17</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-4.33 | Peak: 9.72</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>76829</v>
+        <v>24377</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,67 +1550,67 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-549.70</t>
+          <t>-205.14</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.1705, R2: 0.72)</t>
+          <t>(Eğim: 0.0307, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>KGYO</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>76829</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CEMZY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>24377</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>281,615.56</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %2.79 | Peak: 3.70</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>121,576.54</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %16.90 | Peak: 4.77</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>52835</v>
+        <v>1283</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>94.75</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,32 +1620,32 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-558.21</t>
+          <t>-230.84</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0342, R2: 0.91)</t>
+          <t>(Eğim: 0.0355, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>ISGSY</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>52835</v>
+        <v>1283</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1655,32 +1655,32 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>308,962.95</t>
+          <t>115,008.22</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>P/L: %10.13 | Peak: 6.19</t>
+          <t>P/L: %-5.01 | Peak: 94.75</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>52455</v>
+        <v>5887</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1690,67 +1690,67 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-614.91</t>
+          <t>-215.77</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0354, R2: 0.92)</t>
+          <t>(Eğim: 0.0309, R2: 0.80)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>52455</v>
+        <v>5887</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>299,525.60</t>
+          <t>126,001.73</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-2.66 | Peak: 6.00</t>
+          <t>P/L: %9.98 | Peak: 21.48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>4275</v>
+        <v>5332</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,67 +1760,67 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>-537.09</t>
+          <t>-231.55</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0420, R2: 0.85)</t>
+          <t>(Eğim: 0.0379, R2: 0.79)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>EMKEL</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>4275</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>76.20</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>324,566.38</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %8.78 | Peak: 76.20</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>5332</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>163,396.43</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %30.14 | Peak: 31.41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>8897</v>
+        <v>8541</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,32 +1830,32 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>-645.30</t>
+          <t>-319.67</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0324, R2: 0.83)</t>
+          <t>(Eğim: 0.1055, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>8897</v>
+        <v>8541</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>312,790.67</t>
+          <t>191,638.97</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-3.23 | Peak: 36.92</t>
+          <t>P/L: %17.72 | Peak: 23.14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>38426</v>
+        <v>8734</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,32 +1900,32 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-622.56</t>
+          <t>-368.25</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0537, R2: 0.96)</t>
+          <t>(Eğim: 0.1058, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>38426</v>
+        <v>8734</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1935,32 +1935,32 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>313,456.94</t>
+          <t>180,935.61</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>P/L: %0.61 | Peak: 8.40</t>
+          <t>P/L: %-5.20 | Peak: 21.94</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>34828</v>
+        <v>8376</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>21.60</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,67 +1970,67 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-621.96</t>
+          <t>-347.83</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0381, R2: 0.94)</t>
+          <t>(Eğim: 0.0908, R2: 0.65)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>34828</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>8.61</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>POLHO</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>8376</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>19.86</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>298,647.37</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-4.33 | Peak: 9.72</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>165,666.84</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-8.06 | Peak: 21.60</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>69743</v>
+        <v>4231</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,67 +2040,67 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-597.14</t>
+          <t>-314.77</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0307, R2: 0.91)</t>
+          <t>(Eğim: 0.0458, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>CEMZY</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>69743</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>347,817.11</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %16.90 | Peak: 4.77</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>4231</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>45.49</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>191,757.10</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %16.18 | Peak: 47.27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>RODRG</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>10235</v>
+        <v>17755</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,32 +2110,32 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-663.75</t>
+          <t>-380.41</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0374, R2: 0.91)</t>
+          <t>(Eğim: 0.0304, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>RODRG</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>10235</v>
+        <v>17755</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>31.40</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2145,32 +2145,32 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>320,072.49</t>
+          <t>196,305.94</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-7.59 | Peak: 34.80</t>
+          <t>P/L: %2.78 | Peak: 11.33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>RODRG</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>9983</v>
+        <v>485</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,32 +2180,32 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-622.62</t>
+          <t>-25.94</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0323, R2: 0.83)</t>
+          <t>(Eğim: 0.0337, R2: 0.78)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>RODRG</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>9983</v>
+        <v>485</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>404.25</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2215,32 +2215,32 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>286,910.55</t>
+          <t>195,643.19</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.98 | Peak: 32.06</t>
+          <t>P/L: %0.06 | Peak: 418.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17943</v>
+        <v>4891</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2250,67 +2250,67 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-571.83</t>
+          <t>-388.09</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0308, R2: 0.80)</t>
+          <t>(Eğim: 0.0395, R2: 0.98)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>17943</v>
+        <v>4891</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>41.50</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>257,290.60</t>
+          <t>202,182.45</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.94 | Peak: 15.99</t>
+          <t>P/L: %3.75 | Peak: 41.30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>16243</v>
+        <v>108</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>1861.00</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2320,67 +2320,67 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-513.10</t>
+          <t>792.48</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0352, R2: 0.84)</t>
+          <t>(Eğim: 0.0549, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>ALKA</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>16243</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>14.26</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>230,648.83</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.97 | Peak: 15.84</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>1825.00</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>197,498.28</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.93 | Peak: 1862.00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>16835</v>
+        <v>104</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>1890.00</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,67 +2390,67 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-451.94</t>
+          <t>545.16</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0355, R2: 0.84)</t>
+          <t>(Eğim: 0.0476, R2: 0.86)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>16835</v>
+        <v>104</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>1856.00</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>231,742.43</t>
+          <t>193,183.11</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>P/L: %0.88 | Peak: 15.35</t>
+          <t>P/L: %-1.80 | Peak: 1890.00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>18688</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>1765.00</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2460,67 +2460,67 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-452.22</t>
+          <t>413.34</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0317, R2: 0.92)</t>
+          <t>(Eğim: 0.0376, R2: 0.73)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>18688</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>1711.00</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>223,355.27</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-3.23 | Peak: 13.33</t>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>186,539.34</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-3.06 | Peak: 1765.00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>20681</v>
+        <v>3723</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2530,67 +2530,67 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-446.25</t>
+          <t>-356.00</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0304, R2: 0.87)</t>
+          <t>(Eğim: 0.0340, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>CRDFA</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>20681</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>228,653.74</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %2.78 | Peak: 11.33</t>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3723</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>56.15</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>208,272.36</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %12.08 | Peak: 56.30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>5623</v>
+        <v>3719</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2600,67 +2600,67 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-434.70</t>
+          <t>-408.16</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0337, R2: 0.86)</t>
+          <t>(Eğim: 0.0324, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>DOGUB</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>5623</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>65.35</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3719</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>58.05</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>366,293.42</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %60.72 | Peak: 59.45</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>215,048.01</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %3.66 | Peak: 58.00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>6224</v>
+        <v>1194</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>58.85</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2670,32 +2670,32 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-721.54</t>
+          <t>-301.83</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0596, R2: 0.96)</t>
+          <t>(Eğim: 0.0407, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>6224</v>
+        <v>1194</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>186.80</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2705,32 +2705,32 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>328,490.72</t>
+          <t>222,291.29</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.94 | Peak: 58.85</t>
+          <t>P/L: %3.78 | Peak: 207.50</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>6886</v>
+        <v>1154</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>47.70</t>
+          <t>192.60</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2740,67 +2740,67 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>-628.41</t>
+          <t>-413.63</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0500, R2: 0.87)</t>
+          <t>(Eğim: 0.0522, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>DOGUB</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>6886</v>
+        <v>1154</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>178.80</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>430,603.89</t>
+          <t>205,508.90</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>P/L: %31.55 | Peak: 69.70</t>
+          <t>P/L: %-7.17 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>1713</v>
+        <v>1045</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>251.25</t>
+          <t>196.60</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2810,67 +2810,67 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>-648.14</t>
+          <t>-349.00</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0385, R2: 0.74)</t>
+          <t>(Eğim: 0.0483, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>1713</v>
+        <v>1045</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>247.90</t>
+          <t>229.90</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>VOLUME STOP</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>423,155.25</t>
+          <t>239,416.00</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-1.33 | Peak: 251.25</t>
+          <t>P/L: %16.94 | Peak: 255.25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>40185</v>
+        <v>1095</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>218.50</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2880,54 +2880,54 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>-839.09</t>
+          <t>-320.01</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.81)</t>
+          <t>(Eğim: 0.0362, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>40185</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>196.70</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>405,821.87</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-3.70 | Peak: 10.53</t>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>214,635.71</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.98 | Peak: 218.50</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
@@ -2936,11 +2936,11 @@
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>38466</v>
+        <v>28256</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2950,67 +2950,67 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>-806.07</t>
+          <t>-427.24</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0328, R2: 0.78)</t>
+          <t>(Eğim: 0.0367, R2: 0.77)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>MANAS</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>38466</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>28256</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>6.84</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>363,890.08</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.95 | Peak: 10.55</t>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>192,492.59</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.94 | Peak: 7.60</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>2140</v>
+        <v>3070</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3020,67 +3020,67 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>-637.52</t>
+          <t>-381.39</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0311, R2: 0.67)</t>
+          <t>(Eğim: 0.0302, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>2140</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>186.80</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ARMGD</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>3070</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>72.45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>398,314.98</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %9.88 | Peak: 207.50</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>221,595.26</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %15.55 | Peak: 65.90</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>2068</v>
+        <v>723</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>192.60</t>
+          <t>306.25</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -3090,67 +3090,67 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>-778.42</t>
+          <t>-266.33</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0522, R2: 0.95)</t>
+          <t>(Eğim: 0.0333, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2068</v>
+        <v>723</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>178.80</t>
+          <t>436.25</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>368,240.46</t>
+          <t>314,511.61</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-7.17 | Peak: 192.60</t>
+          <t>P/L: %42.45 | Peak: 396.75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>1873</v>
+        <v>720</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>196.60</t>
+          <t>436.75</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -3160,32 +3160,32 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-727.81</t>
+          <t>-577.31</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0483, R2: 0.91)</t>
+          <t>(Eğim: 0.0302, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>1873</v>
+        <v>720</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>229.90</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3195,32 +3195,32 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>429,013.67</t>
+          <t>286,846.69</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>P/L: %16.94 | Peak: 255.25</t>
+          <t>P/L: %-8.41 | Peak: 442.00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>1963</v>
+        <v>34148</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>218.50</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -3230,67 +3230,67 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>-759.66</t>
+          <t>-570.19</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0362, R2: 0.85)</t>
+          <t>(Eğim: 0.0315, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>1963</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>196.70</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>EDATA</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>34148</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>384,590.19</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.98 | Peak: 218.50</t>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>267,296.29</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-6.43 | Peak: 8.40</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>27102</v>
+        <v>32756</v>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3300,67 +3300,67 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>-756.33</t>
+          <t>-527.24</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0367, R2: 0.77)</t>
+          <t>(Eğim: 0.0317, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>27102</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>EDATA</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>32756</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>344,914.49</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-9.94 | Peak: 14.19</t>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>264,592.60</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-0.61 | Peak: 8.35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>5501</v>
+        <v>2767</v>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>95.60</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -3370,67 +3370,67 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>-688.04</t>
+          <t>-461.64</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0302, R2: 0.87)</t>
+          <t>(Eğim: 0.0343, R2: 0.97)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>ARMGD</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>5501</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>72.45</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>397,062.30</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %15.55 | Peak: 65.90</t>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>TCKRC</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>2767</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>99.75</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>274,994.59</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.34 | Peak: 104.80</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>611</v>
+        <v>8963</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>649.00</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -3440,32 +3440,32 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>-269.78</t>
+          <t>-540.22</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0308, R2: 0.88)</t>
+          <t>(Eğim: 0.0411, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>BURVA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>611</v>
+        <v>8963</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>630.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3475,32 +3475,32 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>383,890.36</t>
+          <t>312,537.37</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-2.93 | Peak: 649.00</t>
+          <t>P/L: %14.08 | Peak: 36.32</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45701</v>
+        <v>8117</v>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>38.50</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -3510,67 +3510,67 @@
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>-765.79</t>
+          <t>-592.14</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0313, R2: 0.86)</t>
+          <t>(Eğim: 0.0406, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>45701</v>
+        <v>8117</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>357,725.65</t>
+          <t>342,394.29</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-6.43 | Peak: 8.40</t>
+          <t>P/L: %9.97 | Peak: 42.34</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>43838</v>
+        <v>7353</v>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3580,67 +3580,67 @@
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>-707.86</t>
+          <t>-646.11</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0324, R2: 0.89)</t>
+          <t>(Eğim: 0.0401, R2: 0.85)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>EDATA</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>43838</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>7353</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>46.08</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>354,107.25</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-0.61 | Peak: 8.35</t>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>337,502.49</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.03 | Peak: 51.20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>39698</v>
+        <v>585</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>576.50</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3650,67 +3650,67 @@
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>-707.12</t>
+          <t>-424.51</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0300, R2: 0.84)</t>
+          <t>(Eğim: 0.0317, R2: 0.89)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>EDATA</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v>39698</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>8.90</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>585</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>519.00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>351,898.44</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-0.22 | Peak: 9.27</t>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>302,583.26</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.97 | Peak: 576.50</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>3587</v>
+        <v>16111</v>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>98.10</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3720,32 +3720,32 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>-690.02</t>
+          <t>-586.46</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0337, R2: 0.96)</t>
+          <t>(Eğim: 0.0414, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>3587</v>
+        <v>16111</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3755,32 +3755,32 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>339,393.45</t>
+          <t>308,930.01</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-3.16 | Peak: 98.10</t>
+          <t>P/L: %2.50 | Peak: 20.46</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>10278</v>
+        <v>5402</v>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -3790,67 +3790,67 @@
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>-664.88</t>
+          <t>-595.99</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0418, R2: 0.86)</t>
+          <t>(Eğim: 0.0313, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>10278</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>358,345.66</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %6.00 | Peak: 36.32</t>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>5402</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>67.13</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>361,294.87</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %17.39 | Peak: 65.44</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>9307</v>
+        <v>5315</v>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>67.97</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3860,67 +3860,67 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>-690.48</t>
+          <t>-693.69</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0406, R2: 0.85)</t>
+          <t>(Eğim: 0.0346, R2: 0.95)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>9307</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>392,579.79</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %9.97 | Peak: 42.34</t>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>HEDEF</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>5315</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>73.88</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (7D)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>391,216.38</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %8.70 | Peak: 73.88</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>ODINE</t>
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>8431</v>
+        <v>615</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>636.00</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3930,67 +3930,67 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>-752.68</t>
+          <t>-705.90</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0401, R2: 0.85)</t>
+          <t>(Eğim: 0.0346, R2: 0.94)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>ODINE</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>8431</v>
+        <v>615</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>386,970.82</t>
+          <t>398,244.60</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-1.03 | Peak: 51.20</t>
+          <t>P/L: %2.20 | Peak: 679.00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>8088</v>
+        <v>544</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>731.50</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -4000,67 +4000,67 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>-732.96</t>
+          <t>-487.27</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0350, R2: 0.84)</t>
+          <t>(Eğim: 0.0438, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>SEGMN</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>8088</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>46.20</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>STOP LOSS</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>372,185.31</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-3.43 | Peak: 47.84</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>544</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>719.00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>389,866.46</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.71 | Peak: 731.50</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>17842</v>
+        <v>602</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>647.50</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -4070,67 +4070,67 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>-743.19</t>
+          <t>-708.13</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0438, R2: 0.97)</t>
+          <t>(Eğim: 0.0343, R2: 0.82)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>17842</v>
+        <v>602</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>647.50</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>333,659.44</t>
+          <t>388,307.28</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-9.97 | Peak: 20.86</t>
+          <t>P/L: %0.00 | Peak: 647.50</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>17938</v>
+        <v>908</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>18.60</t>
+          <t>427.50</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -4140,32 +4140,32 @@
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>-654.66</t>
+          <t>-639.06</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0379, R2: 0.89)</t>
+          <t>(Eğim: 0.0378, R2: 0.92)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>17938</v>
+        <v>908</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>425.00</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -4175,32 +4175,32 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>343,961.22</t>
+          <t>384,489.14</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>P/L: %3.49 | Peak: 20.46</t>
+          <t>P/L: %-0.58 | Peak: 439.00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>NIBAS</t>
+          <t>AKFIS</t>
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>51723</v>
+        <v>9359</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -4210,32 +4210,32 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>-684.65</t>
+          <t>-747.54</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0326, R2: 0.86)</t>
+          <t>(Eğim: 0.0301, R2: 0.90)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>NIBAS</t>
+          <t>AKFIS</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>51723</v>
+        <v>9359</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>43.50</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4245,32 +4245,32 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>325,550.94</t>
+          <t>405,554.73</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-4.96 | Peak: 6.65</t>
+          <t>P/L: %5.89 | Peak: 45.18</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>NIBAS</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>49778</v>
+        <v>6932</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>58.50</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -4280,32 +4280,32 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>-648.27</t>
+          <t>-778.31</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0363, R2: 0.91)</t>
+          <t>(Eğim: 0.0423, R2: 0.76)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>NIBAS</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>49778</v>
+        <v>6932</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>53.10</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -4315,32 +4315,32 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>329,713.39</t>
+          <t>366,574.70</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>P/L: %1.68 | Peak: 7.10</t>
+          <t>P/L: %-9.23 | Peak: 59.00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>DSTKF</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>219</v>
+        <v>7331</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -4350,67 +4350,67 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>556.39</t>
+          <t>-708.40</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0376, R2: 0.93)</t>
+          <t>(Eğim: 0.0513, R2: 0.91)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>DSTKF</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>1731.00</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (7D)</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>378,887.21</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %15.40 | Peak: 1730.00</t>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>MARKA</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>7331</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>60.50</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>441,930.05</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %21.00 | Peak: 60.50</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>ODINE</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>591</v>
+        <v>7150</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>641.00</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4420,32 +4420,32 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>-701.45</t>
+          <t>-823.69</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0323, R2: 0.91)</t>
+          <t>(Eğim: 0.0456, R2: 0.88)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ODINE</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>591</v>
+        <v>7150</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>650.00</t>
+          <t>59.40</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4455,32 +4455,32 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>382,680.25</t>
+          <t>423,036.90</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>P/L: %1.40 | Peak: 679.00</t>
+          <t>P/L: %-3.88 | Peak: 61.80</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>523</v>
+        <v>7038</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>731.50</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4490,67 +4490,67 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>-659.40</t>
+          <t>-792.85</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0438, R2: 0.91)</t>
+          <t>(Eğim: 0.0359, R2: 0.84)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>523</v>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>719.00</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>VOLUME STOP</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>374,625.52</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-1.71 | Peak: 731.50</t>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>MARKA</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>7038</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>58.40</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>409,404.32</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-2.83 | Peak: 60.10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>578</v>
+        <v>2762</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>647.50</t>
+          <t>148.20</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4560,67 +4560,67 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>-377.99</t>
+          <t>-742.73</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0343, R2: 0.82)</t>
+          <t>(Eğim: 0.0420, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>578</v>
+        <v>2762</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>831.50</t>
+          <t>145.20</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>479,267.80</t>
+          <t>399,497.58</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>P/L: %28.42 | Peak: 760.00</t>
+          <t>P/L: %-2.02 | Peak: 148.20</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>3238</v>
+        <v>2861</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>147.97</t>
+          <t>139.60</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -4630,67 +4630,67 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>-827.71</t>
+          <t>-696.83</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0302, R2: 0.83)</t>
+          <t>(Eğim: 0.0362, R2: 0.83)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>NETCD</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>3238</v>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>142.75</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>ARMGD</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>2861</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>130.20</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>STOP LOSS</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>460,474.36</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %-3.53 | Peak: 158.52</t>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>371,060.36</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-6.73 | Peak: 145.00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>3268</v>
+        <v>7634</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>140.90</t>
+          <t>48.60</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
@@ -4700,67 +4700,67 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>-907.74</t>
+          <t>-694.06</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0303, R2: 0.81)</t>
+          <t>(Eğim: 0.0717, R2: 0.97)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>3268</v>
+        <v>7634</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>148.20</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (7D)</t>
+          <t>STOP LOSS</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>482,441.21</t>
+          <t>332,549.29</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>P/L: %5.18 | Peak: 149.80</t>
+          <t>P/L: %-10.00 | Peak: 48.60</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>3290</v>
+        <v>6913</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>146.60</t>
+          <t>48.10</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -4770,67 +4770,67 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>-837.44</t>
+          <t>-631.03</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0421, R2: 0.93)</t>
+          <t>(Eğim: 0.0665, R2: 0.93)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>3290</v>
+        <v>6913</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>139.60</t>
+          <t>52.90</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>STOP LOSS</t>
+          <t>VOLUME STOP</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>457,528.01</t>
+          <t>364,335.29</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-4.77 | Peak: 147.50</t>
+          <t>P/L: %9.98 | Peak: 52.90</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>3155</v>
+        <v>30849</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>145.00</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>-861.94</t>
+          <t>-720.07</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0327, R2: 0.78)</t>
+          <t>(Eğim: 0.0458, R2: 0.87)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>3155</v>
+        <v>30849</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>130.20</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>409,097.49</t>
+          <t>400,746.35</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>P/L: %-10.21 | Peak: 145.00</t>
+          <t>P/L: %10.41 | Peak: 13.57</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>SVGYO</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>23551</v>
+        <v>7532</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>53.20</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4910,47 +4910,677 @@
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>-801.56</t>
+          <t>-757.46</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>(Eğim: 0.0438, R2: 0.81)</t>
+          <t>(Eğim: 0.0313, R2: 0.75)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>SVGYO</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>23551</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>7532</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>77.80</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (7D)</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>454,233.92</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %11.46 | Peak: 19.23</t>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>584,060.18</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %46.24 | Peak: 77.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>14601</v>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>-1,147.90</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0613, R2: 0.96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>14601</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>523,436.83</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-10.00 | Peak: 40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>14208</v>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>36.84</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>-1,032.74</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0572, R2: 0.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>14208</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>37.00</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>523,611.87</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.43 | Peak: 37.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>12865</v>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>40.70</t>
+        </is>
+      </c>
+      <c r="E134" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>-1,040.85</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0501, R2: 0.89)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>12865</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>40.70</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>521,517.45</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.00 | Peak: 40.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>12813</v>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>40.70</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>-1,014.64</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0447, R2: 0.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>12813</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>40.70</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>519,431.49</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.00 | Peak: 40.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>371</v>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>1400.00</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>-1,007.31</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0603, R2: 0.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>1429.00</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>528,091.37</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %2.07 | Peak: 1429.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>5874</v>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>89.90</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>-1,037.38</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0327, R2: 0.86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>5874</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>89.70</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>524,806.61</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-0.22 | Peak: 89.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>351</v>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>1494.00</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
+          <t>-636.18</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0400, R2: 0.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>351</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>1469.00</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>513,951.58</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.67 | Peak: 1494.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>342</v>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>1502.00</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>-759.79</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0303, R2: 0.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>OZATD</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>1494.00</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME STOP</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>509,166.32</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-0.53 | Peak: 1502.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>HRKET</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>4389</v>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>116.00</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>-975.93</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>(Eğim: 0.0352, R2: 0.89)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>HRKET</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>4389</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>112.00</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>STOP LOSS</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>489,608.93</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-3.45 | Peak: 116.00</t>
         </is>
       </c>
     </row>
